--- a/artfynd/A 17109-2024 artfynd.xlsx
+++ b/artfynd/A 17109-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89564991</v>
+        <v>89564989</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388266.2072162581</v>
+        <v>388252</v>
       </c>
       <c r="R2" t="n">
-        <v>6965363.061549352</v>
+        <v>6965550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89565022</v>
+        <v>89564999</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388251.9361040951</v>
+        <v>388261</v>
       </c>
       <c r="R3" t="n">
-        <v>6965549.866139424</v>
+        <v>6965353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89564999</v>
+        <v>89565019</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388260.8277836858</v>
+        <v>388215</v>
       </c>
       <c r="R4" t="n">
-        <v>6965353.173046634</v>
+        <v>6965348</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89565000</v>
+        <v>89565024</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388264.0836152502</v>
+        <v>387963</v>
       </c>
       <c r="R5" t="n">
-        <v>6965570.052373451</v>
+        <v>6965284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,24 +1046,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89565013</v>
+        <v>89565033</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388242.813469525</v>
+        <v>387942</v>
       </c>
       <c r="R6" t="n">
-        <v>6965349.208208214</v>
+        <v>6965274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,24 +1147,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89564997</v>
+        <v>89565050</v>
       </c>
       <c r="B7" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>387963.0702922425</v>
+        <v>388005</v>
       </c>
       <c r="R7" t="n">
-        <v>6965292.818502359</v>
+        <v>6965241</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,19 +1248,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89565019</v>
+        <v>89565004</v>
       </c>
       <c r="B8" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1421,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388214.8028161903</v>
+        <v>388154</v>
       </c>
       <c r="R8" t="n">
-        <v>6965347.872817732</v>
+        <v>6965421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,19 +1349,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89565029</v>
+        <v>89565009</v>
       </c>
       <c r="B9" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387961.8891650851</v>
+        <v>388221</v>
       </c>
       <c r="R9" t="n">
-        <v>6965285.075999779</v>
+        <v>6965352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,19 +1450,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89565048</v>
+        <v>89565022</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388266.2095817268</v>
+        <v>388252</v>
       </c>
       <c r="R10" t="n">
-        <v>6965390.071483728</v>
+        <v>6965550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,19 +1551,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89565045</v>
+        <v>89565025</v>
       </c>
       <c r="B11" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388265.0692947164</v>
+        <v>387964</v>
       </c>
       <c r="R11" t="n">
-        <v>6965396.977210138</v>
+        <v>6965284</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,19 +1652,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,32 +1685,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89565004</v>
+        <v>89564997</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1885,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388154.0251838383</v>
+        <v>387963</v>
       </c>
       <c r="R12" t="n">
-        <v>6965420.901307911</v>
+        <v>6965293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,19 +1753,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89565050</v>
+        <v>89565029</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388004.8571434031</v>
+        <v>387962</v>
       </c>
       <c r="R13" t="n">
-        <v>6965241.033148831</v>
+        <v>6965285</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,19 +1854,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89564996</v>
+        <v>89565031</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388173.2011098998</v>
+        <v>387942</v>
       </c>
       <c r="R14" t="n">
-        <v>6965405.140905692</v>
+        <v>6965274</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,19 +1955,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89565009</v>
+        <v>89565005</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388220.8958318532</v>
+        <v>387945</v>
       </c>
       <c r="R15" t="n">
-        <v>6965351.785571987</v>
+        <v>6965284</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,19 +2056,14 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,15 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89565025</v>
+        <v>89565013</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,10 +2129,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387964.1475771256</v>
+        <v>388243</v>
       </c>
       <c r="R16" t="n">
-        <v>6965284.083306097</v>
+        <v>6965349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,19 +2162,14 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2425,15 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89564985</v>
+        <v>89565045</v>
       </c>
       <c r="B17" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,21 +2211,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388293.7860577488</v>
+        <v>388265</v>
       </c>
       <c r="R17" t="n">
-        <v>6965594.218776374</v>
+        <v>6965397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,19 +2268,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,37 +2301,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89564994</v>
+        <v>89564985</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388158.1930617187</v>
+        <v>388294</v>
       </c>
       <c r="R18" t="n">
-        <v>6965422.132692782</v>
+        <v>6965594</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2614,19 +2369,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,37 +2402,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89565021</v>
+        <v>89565167</v>
       </c>
       <c r="B19" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2697,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388293.8482934752</v>
+        <v>388552</v>
       </c>
       <c r="R19" t="n">
-        <v>6965596.047723647</v>
+        <v>6965704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,19 +2470,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,16 +2506,11 @@
         <v>89565041</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2813,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388266.2072162581</v>
+        <v>388266</v>
       </c>
       <c r="R20" t="n">
-        <v>6965363.061549352</v>
+        <v>6965363</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,19 +2571,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2889,37 +2604,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89565001</v>
+        <v>89565245</v>
       </c>
       <c r="B21" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2929,10 +2639,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388284.8996038595</v>
+        <v>388552</v>
       </c>
       <c r="R21" t="n">
-        <v>6965589.027976287</v>
+        <v>6965704</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,19 +2672,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3005,15 +2705,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89565028</v>
+        <v>89565001</v>
       </c>
       <c r="B22" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3021,21 +2716,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3045,10 +2740,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387963.2317284831</v>
+        <v>388285</v>
       </c>
       <c r="R22" t="n">
-        <v>6965284.114559088</v>
+        <v>6965589</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3078,19 +2773,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3121,15 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89564989</v>
+        <v>89565000</v>
       </c>
       <c r="B23" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388251.9361040951</v>
+        <v>388264</v>
       </c>
       <c r="R23" t="n">
-        <v>6965549.866139424</v>
+        <v>6965570</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3194,19 +2874,14 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3237,37 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89565024</v>
+        <v>89565021</v>
       </c>
       <c r="B24" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3277,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387963.2317284831</v>
+        <v>388294</v>
       </c>
       <c r="R24" t="n">
-        <v>6965284.114559088</v>
+        <v>6965596</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,19 +2980,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 17109-2024 artfynd.xlsx
+++ b/artfynd/A 17109-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564989</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564985</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565024</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565004</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565009</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565022</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565041</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565245</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565001</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89564997</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565029</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565031</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565000</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,6 +2908,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565005</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565013</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3010,8 +3125,38 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89565021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>